--- a/output/paket/02_MEKANİK/Gym_Mekanik_BoQ.xlsx
+++ b/output/paket/02_MEKANİK/Gym_Mekanik_BoQ.xlsx
@@ -718,7 +718,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rev G · 17 Eylül 2026 · Eylül 2026 · Aqua Florya / Saltbae kesin hakedişi (Mayıs 2025) birim fiyatları ×1,40 eskalasyonla · Ekipman işverence temin edilmiştir, bütçe dışıdır.</t>
+          <t>Rev H · 17 Eylül 2026 · Eylül 2026 · Aqua Florya / Saltbae kesin hakedişi (Mayıs 2025) birim fiyatları ×1,40 eskalasyonla · Ekipman işverence temin edilmiştir, bütçe dışıdır.</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev G · 17 Eylül 2026 · Fiyat referansı: Eylül 2026 · Aqua Florya / Saltbae kesin hakedişi (Mayıs 2025) birim fiyatları ×1,40 eskalasyonla · Birim fiyat sütununu (F) doldurun, tutarlar kendiliğinden hesaplanır</t>
+          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev H · 17 Eylül 2026 · Fiyat referansı: Eylül 2026 · Aqua Florya / Saltbae kesin hakedişi (Mayıs 2025) birim fiyatları ×1,40 eskalasyonla · Birim fiyat sütununu (F) doldurun, tutarlar kendiliğinden hesaplanır</t>
         </is>
       </c>
     </row>

--- a/output/paket/02_MEKANİK/Gym_Mekanik_BoQ.xlsx
+++ b/output/paket/02_MEKANİK/Gym_Mekanik_BoQ.xlsx
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="E8" s="21" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="F8" s="22" t="n"/>
       <c r="G8" s="23">
@@ -1154,10 +1154,10 @@
         <v/>
       </c>
       <c r="H8" s="24" t="n">
-        <v>12075</v>
+        <v>12190</v>
       </c>
       <c r="I8" s="24" t="n">
-        <v>19950</v>
+        <v>20140</v>
       </c>
     </row>
     <row r="9">
@@ -1182,7 +1182,7 @@
         </is>
       </c>
       <c r="E9" s="29" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="F9" s="22" t="n"/>
       <c r="G9" s="30">
@@ -1190,10 +1190,10 @@
         <v/>
       </c>
       <c r="H9" s="31" t="n">
-        <v>2728</v>
+        <v>3162</v>
       </c>
       <c r="I9" s="31" t="n">
-        <v>4620</v>
+        <v>5355</v>
       </c>
     </row>
     <row r="10">
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="E10" s="21" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="F10" s="22" t="n"/>
       <c r="G10" s="23">
@@ -1226,10 +1226,10 @@
         <v/>
       </c>
       <c r="H10" s="24" t="n">
-        <v>1260</v>
+        <v>1050</v>
       </c>
       <c r="I10" s="24" t="n">
-        <v>2160</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="11">
@@ -1254,7 +1254,7 @@
         </is>
       </c>
       <c r="E11" s="29" t="n">
-        <v>15</v>
+        <v>16.7</v>
       </c>
       <c r="F11" s="22" t="n"/>
       <c r="G11" s="30">
@@ -1262,10 +1262,10 @@
         <v/>
       </c>
       <c r="H11" s="31" t="n">
-        <v>8100</v>
+        <v>9018</v>
       </c>
       <c r="I11" s="31" t="n">
-        <v>13500</v>
+        <v>15030</v>
       </c>
     </row>
     <row r="12">
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="E18" s="21" t="n">
-        <v>35.5</v>
+        <v>35.6</v>
       </c>
       <c r="F18" s="22" t="n"/>
       <c r="G18" s="23">
@@ -1514,10 +1514,10 @@
         <v/>
       </c>
       <c r="H18" s="24" t="n">
-        <v>27690</v>
+        <v>27768</v>
       </c>
       <c r="I18" s="24" t="n">
-        <v>46150</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="19">
@@ -1542,7 +1542,7 @@
         </is>
       </c>
       <c r="E19" s="29" t="n">
-        <v>42.3</v>
+        <v>44.1</v>
       </c>
       <c r="F19" s="22" t="n"/>
       <c r="G19" s="30">
@@ -1550,10 +1550,10 @@
         <v/>
       </c>
       <c r="H19" s="31" t="n">
-        <v>13536</v>
+        <v>14112</v>
       </c>
       <c r="I19" s="31" t="n">
-        <v>22842</v>
+        <v>23814</v>
       </c>
     </row>
     <row r="20">
@@ -1758,7 +1758,7 @@
         </is>
       </c>
       <c r="E25" s="29" t="n">
-        <v>35.8</v>
+        <v>34</v>
       </c>
       <c r="F25" s="22" t="n"/>
       <c r="G25" s="30">
@@ -1766,10 +1766,10 @@
         <v/>
       </c>
       <c r="H25" s="31" t="n">
-        <v>39380</v>
+        <v>37400</v>
       </c>
       <c r="I25" s="31" t="n">
-        <v>66230</v>
+        <v>62900</v>
       </c>
     </row>
     <row r="26">
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="E27" s="29" t="n">
-        <v>34.2</v>
+        <v>31.9</v>
       </c>
       <c r="F27" s="22" t="n"/>
       <c r="G27" s="30">
@@ -1838,10 +1838,10 @@
         <v/>
       </c>
       <c r="H27" s="31" t="n">
-        <v>14364</v>
+        <v>13398</v>
       </c>
       <c r="I27" s="31" t="n">
-        <v>24624</v>
+        <v>22968</v>
       </c>
     </row>
     <row r="28">
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="B13" s="42" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         </is>
       </c>
       <c r="B14" s="44" t="n">
-        <v>15</v>
+        <v>16.7</v>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="B15" s="42" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="B16" s="44" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="B23" s="42" t="n">
-        <v>35.8</v>
+        <v>34</v>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         </is>
       </c>
       <c r="B24" s="44" t="n">
-        <v>34.2</v>
+        <v>31.9</v>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>

--- a/output/paket/02_MEKANİK/Gym_Mekanik_BoQ.xlsx
+++ b/output/paket/02_MEKANİK/Gym_Mekanik_BoQ.xlsx
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="E10" s="21" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="F10" s="22" t="n"/>
       <c r="G10" s="23">
@@ -1226,10 +1226,10 @@
         <v/>
       </c>
       <c r="H10" s="24" t="n">
-        <v>1050</v>
+        <v>1260</v>
       </c>
       <c r="I10" s="24" t="n">
-        <v>1800</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="11">
@@ -1254,7 +1254,7 @@
         </is>
       </c>
       <c r="E11" s="29" t="n">
-        <v>16.7</v>
+        <v>13.9</v>
       </c>
       <c r="F11" s="22" t="n"/>
       <c r="G11" s="30">
@@ -1262,10 +1262,10 @@
         <v/>
       </c>
       <c r="H11" s="31" t="n">
-        <v>9018</v>
+        <v>7506</v>
       </c>
       <c r="I11" s="31" t="n">
-        <v>15030</v>
+        <v>12510</v>
       </c>
     </row>
     <row r="12">
@@ -1542,7 +1542,7 @@
         </is>
       </c>
       <c r="E19" s="29" t="n">
-        <v>44.1</v>
+        <v>41.3</v>
       </c>
       <c r="F19" s="22" t="n"/>
       <c r="G19" s="30">
@@ -1550,10 +1550,10 @@
         <v/>
       </c>
       <c r="H19" s="31" t="n">
-        <v>14112</v>
+        <v>13216</v>
       </c>
       <c r="I19" s="31" t="n">
-        <v>23814</v>
+        <v>22302</v>
       </c>
     </row>
     <row r="20">
@@ -2514,7 +2514,7 @@
         </is>
       </c>
       <c r="B14" s="44" t="n">
-        <v>16.7</v>
+        <v>13.9</v>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="B16" s="44" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
